--- a/Scenario Files/ApplianceRAGScenarios.xlsx
+++ b/Scenario Files/ApplianceRAGScenarios.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2604</v>
+        <v>0.279</v>
       </c>
       <c r="R2" t="n">
         <v>2.915</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -632,13 +632,13 @@
         <v>0.82</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5760000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2604</v>
+        <v>0.279</v>
       </c>
       <c r="R3" t="n">
         <v>2.915</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="L4" t="n">
         <v>0.22</v>
@@ -700,13 +700,13 @@
         <v>0.54</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3760000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.518</v>
+        <v>0.5523</v>
       </c>
       <c r="R4" t="n">
         <v>2.915</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -768,13 +768,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.518</v>
+        <v>0.521</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3255</v>
+        <v>0.3487</v>
       </c>
       <c r="R5" t="n">
         <v>3.643</v>
@@ -786,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -836,13 +836,13 @@
         <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4245000000000001</v>
+        <v>0.4275</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3255</v>
+        <v>0.3487</v>
       </c>
       <c r="R6" t="n">
         <v>3.643</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -904,13 +904,13 @@
         <v>0.43</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2095</v>
+        <v>0.2155</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6475</v>
+        <v>0.6904</v>
       </c>
       <c r="R7" t="n">
         <v>3.643</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L8" t="n">
         <v>0.98</v>
@@ -972,13 +972,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.993</v>
+        <v>0.987</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0245</v>
+        <v>0.042</v>
       </c>
       <c r="R8" t="n">
         <v>0.364</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L9" t="n">
         <v>0.98</v>
@@ -1040,13 +1040,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8499999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.056</v>
+        <v>0.042</v>
       </c>
       <c r="R9" t="n">
         <v>0.364</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L10" t="n">
         <v>0.98</v>
@@ -1108,13 +1108,13 @@
         <v>0.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7415</v>
+        <v>0.7355</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0245</v>
+        <v>0.042</v>
       </c>
       <c r="R10" t="n">
         <v>0.342</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1182,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="R11" t="n">
         <v>1.145</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="L12" t="n">
         <v>0.74</v>
@@ -1244,13 +1244,13 @@
         <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6805</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.352</v>
+        <v>0.3602</v>
       </c>
       <c r="R12" t="n">
         <v>1.145</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1318,7 +1318,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="R13" t="n">
         <v>1.145</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>0.95</v>
@@ -1380,13 +1380,13 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9794999999999999</v>
+        <v>0.9735</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0315</v>
+        <v>0.049</v>
       </c>
       <c r="R14" t="n">
         <v>0.468</v>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L15" t="n">
         <v>0.95</v>
@@ -1448,13 +1448,13 @@
         <v>0.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7685</v>
+        <v>0.7415</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0315</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="R15" t="n">
         <v>0.468</v>
@@ -1522,7 +1522,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0315</v>
+        <v>0.0363</v>
       </c>
       <c r="R16" t="n">
         <v>0.439</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L17" t="n">
         <v>0.22</v>
@@ -1584,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L18" t="n">
         <v>0.22</v>
@@ -1652,7 +1652,7 @@
         <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0.454</v>
+        <v>0.469</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L19" t="n">
         <v>0.27</v>
@@ -1720,7 +1720,7 @@
         <v>0.21</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3129999999999999</v>
+        <v>0.328</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.032</v>
+        <v>0.0365</v>
       </c>
       <c r="R20" t="n">
         <v>0.208</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1862,7 +1862,7 @@
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.014</v>
+        <v>0.0187</v>
       </c>
       <c r="R21" t="n">
         <v>0.208</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1924,13 +1924,13 @@
         <v>0.29</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7654999999999998</v>
+        <v>0.7655</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.014</v>
+        <v>0.0138</v>
       </c>
       <c r="R22" t="n">
         <v>0.195</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1992,13 +1992,13 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9939999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0368</v>
+        <v>0.0322</v>
       </c>
       <c r="R23" t="n">
         <v>0.239</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2060,13 +2060,13 @@
         <v>0.43</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8324999999999999</v>
+        <v>0.8325</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
       <c r="R24" t="n">
         <v>0.239</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2128,13 +2128,13 @@
         <v>0.52</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8479999999999999</v>
+        <v>0.848</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
       <c r="R25" t="n">
         <v>0.239</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2196,13 +2196,13 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.554</v>
+        <v>0.464</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.245</v>
+        <v>0.4895</v>
       </c>
       <c r="R26" t="n">
         <v>3.643</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>0.34</v>
       </c>
       <c r="O27" t="n">
-        <v>0.357</v>
+        <v>0.297</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R27" t="n">
         <v>3.643</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L28" t="n">
         <v>0.07000000000000001</v>
@@ -2332,13 +2332,13 @@
         <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>0.389</v>
+        <v>0.329</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R28" t="n">
         <v>3.416</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="L29" t="n">
         <v>0.86</v>
@@ -2400,13 +2400,13 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8610000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2304</v>
+        <v>0.2358</v>
       </c>
       <c r="R29" t="n">
         <v>0.75</v>
@@ -2474,7 +2474,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0547</v>
+        <v>0.0604</v>
       </c>
       <c r="R30" t="n">
         <v>0.75</v>
@@ -2542,7 +2542,7 @@
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0547</v>
+        <v>0.0604</v>
       </c>
       <c r="R31" t="n">
         <v>0.75</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.19</v>
+        <v>0.2096</v>
       </c>
       <c r="R32" t="n">
         <v>2.603</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2678,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.19</v>
+        <v>0.2096</v>
       </c>
       <c r="R33" t="n">
         <v>2.603</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2746,7 +2746,7 @@
         <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8</v>
+        <v>0.8187</v>
       </c>
       <c r="R34" t="n">
         <v>2.603</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0.95</v>
@@ -2808,13 +2808,13 @@
         <v>0.93</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9319999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0396</v>
+        <v>0.031</v>
       </c>
       <c r="R35" t="n">
         <v>0.439</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2876,13 +2876,13 @@
         <v>0.39</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0396</v>
+        <v>0.0421</v>
       </c>
       <c r="R36" t="n">
         <v>0.468</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L37" t="n">
         <v>0.95</v>
@@ -2944,13 +2944,13 @@
         <v>0.43</v>
       </c>
       <c r="O37" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0774</v>
+        <v>0.082</v>
       </c>
       <c r="R37" t="n">
         <v>0.468</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="L38" t="n">
         <v>0.31</v>
@@ -3012,13 +3012,13 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.5935</v>
+        <v>0.6505</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.2997</v>
       </c>
       <c r="R38" t="n">
         <v>2.603</v>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="L39" t="n">
         <v>0.31</v>
@@ -3080,13 +3080,13 @@
         <v>0.8</v>
       </c>
       <c r="O39" t="n">
-        <v>0.5375</v>
+        <v>0.5735</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4</v>
+        <v>0.3497</v>
       </c>
       <c r="R39" t="n">
         <v>2.603</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="L40" t="n">
         <v>0.31</v>
@@ -3148,13 +3148,13 @@
         <v>0.46</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5335</v>
+        <v>0.4915</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.175</v>
+        <v>0.2997</v>
       </c>
       <c r="R40" t="n">
         <v>2.603</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="L41" t="n">
         <v>0.74</v>
@@ -3216,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8850000000000001</v>
+        <v>0.873</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.077</v>
+        <v>0.1198</v>
       </c>
       <c r="R41" t="n">
         <v>1.145</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="L42" t="n">
         <v>0.74</v>
@@ -3284,13 +3284,13 @@
         <v>0.58</v>
       </c>
       <c r="O42" t="n">
-        <v>0.722</v>
+        <v>0.701</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.176</v>
+        <v>0.2433</v>
       </c>
       <c r="R42" t="n">
         <v>1.145</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="L43" t="n">
         <v>0.74</v>
@@ -3352,13 +3352,13 @@
         <v>0.3</v>
       </c>
       <c r="O43" t="n">
-        <v>0.676</v>
+        <v>0.613</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.077</v>
+        <v>0.2433</v>
       </c>
       <c r="R43" t="n">
         <v>1.145</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L44" t="n">
         <v>0.98</v>
@@ -3420,13 +3420,13 @@
         <v>0.85</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9265000000000001</v>
+        <v>0.9205</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R44" t="n">
         <v>0.371</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L45" t="n">
         <v>0.97</v>
@@ -3488,13 +3488,13 @@
         <v>0.35</v>
       </c>
       <c r="O45" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R45" t="n">
         <v>0.396</v>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L46" t="n">
         <v>0.97</v>
@@ -3556,13 +3556,13 @@
         <v>0.2</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7415</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0608</v>
+        <v>0.0456</v>
       </c>
       <c r="R46" t="n">
         <v>0.396</v>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3624,13 +3624,13 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.6595000000000001</v>
+        <v>0.6595</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.25</v>
+        <v>0.2722</v>
       </c>
       <c r="R47" t="n">
         <v>2.603</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3692,13 +3692,13 @@
         <v>0.67</v>
       </c>
       <c r="O48" t="n">
-        <v>0.4550000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5075</v>
+        <v>0.553</v>
       </c>
       <c r="R48" t="n">
         <v>2.603</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="L49" t="n">
         <v>0.36</v>
@@ -3760,13 +3760,13 @@
         <v>0.15</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4075</v>
+        <v>0.4375</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.25</v>
+        <v>0.2014</v>
       </c>
       <c r="R49" t="n">
         <v>2.44</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0.99</v>
@@ -3828,13 +3828,13 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9934999999999999</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.032</v>
+        <v>0.0299</v>
       </c>
       <c r="R50" t="n">
         <v>0.333</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L51" t="n">
         <v>0.99</v>
@@ -3896,13 +3896,13 @@
         <v>0.62</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8694999999999999</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.065</v>
+        <v>0.0583</v>
       </c>
       <c r="R51" t="n">
         <v>0.333</v>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0.99</v>
@@ -3964,13 +3964,13 @@
         <v>0.22</v>
       </c>
       <c r="O52" t="n">
-        <v>0.7065</v>
+        <v>0.7095</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.032</v>
+        <v>0.0299</v>
       </c>
       <c r="R52" t="n">
         <v>0.333</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.048</v>
+        <v>0.0491</v>
       </c>
       <c r="R53" t="n">
         <v>0.156</v>
@@ -4100,13 +4100,13 @@
         <v>0.62</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8909999999999999</v>
+        <v>0.891</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="R54" t="n">
         <v>0.156</v>
@@ -4168,13 +4168,13 @@
         <v>0.41</v>
       </c>
       <c r="O55" t="n">
-        <v>0.7834999999999999</v>
+        <v>0.7835</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="R55" t="n">
         <v>0.146</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L56" t="n">
         <v>0.36</v>
@@ -4236,7 +4236,7 @@
         <v>0.85</v>
       </c>
       <c r="O56" t="n">
-        <v>0.5685</v>
+        <v>0.5835</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L57" t="n">
         <v>0.31</v>
@@ -4304,7 +4304,7 @@
         <v>0.39</v>
       </c>
       <c r="O57" t="n">
-        <v>0.4360000000000001</v>
+        <v>0.451</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L58" t="n">
         <v>0.31</v>
@@ -4372,7 +4372,7 @@
         <v>0.34</v>
       </c>
       <c r="O58" t="n">
-        <v>0.4205</v>
+        <v>0.4355</v>
       </c>
       <c r="P58" t="n">
         <v>3</v>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L59" t="n">
         <v>0.96</v>
@@ -4440,13 +4440,13 @@
         <v>0.93</v>
       </c>
       <c r="O59" t="n">
-        <v>0.9255</v>
+        <v>0.9285</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.0391</v>
+        <v>0.0321</v>
       </c>
       <c r="R59" t="n">
         <v>0.41</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4508,13 +4508,13 @@
         <v>0.3</v>
       </c>
       <c r="O60" t="n">
-        <v>0.7689999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="P60" t="n">
         <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0391</v>
+        <v>0.0418</v>
       </c>
       <c r="R60" t="n">
         <v>0.437</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L61" t="n">
         <v>0.96</v>
@@ -4576,13 +4576,13 @@
         <v>0.43</v>
       </c>
       <c r="O61" t="n">
-        <v>0.7945</v>
+        <v>0.7975</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0828</v>
       </c>
       <c r="R61" t="n">
         <v>0.437</v>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>0.74</v>
@@ -4644,13 +4644,13 @@
         <v>0.85</v>
       </c>
       <c r="O62" t="n">
-        <v>0.8565</v>
+        <v>0.8685</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0912</v>
+        <v>0.0727</v>
       </c>
       <c r="R62" t="n">
         <v>1.171</v>
@@ -4718,7 +4718,7 @@
         <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R63" t="n">
         <v>1.249</v>
@@ -4786,7 +4786,7 @@
         <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R64" t="n">
         <v>1.249</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L65" t="n">
         <v>0.76</v>
@@ -4848,13 +4848,13 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.847</v>
+        <v>0.85</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1806</v>
+        <v>0.1914</v>
       </c>
       <c r="R65" t="n">
         <v>1.093</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="L66" t="n">
         <v>0.76</v>
@@ -4916,13 +4916,13 @@
         <v>0.58</v>
       </c>
       <c r="O66" t="n">
-        <v>0.765</v>
+        <v>0.768</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0924</v>
+        <v>0.0982</v>
       </c>
       <c r="R66" t="n">
         <v>1.093</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L67" t="n">
         <v>0.78</v>
@@ -4984,13 +4984,13 @@
         <v>0.34</v>
       </c>
       <c r="O67" t="n">
-        <v>0.718</v>
+        <v>0.73</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.0924</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="R67" t="n">
         <v>1.025</v>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L68" t="n">
         <v>0.51</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.7295</v>
+        <v>0.7385</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L69" t="n">
         <v>0.51</v>
@@ -5120,7 +5120,7 @@
         <v>0.58</v>
       </c>
       <c r="O69" t="n">
-        <v>0.6084999999999999</v>
+        <v>0.6175</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L70" t="n">
         <v>0.55</v>
@@ -5188,7 +5188,7 @@
         <v>0.29</v>
       </c>
       <c r="O70" t="n">
-        <v>0.551</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P70" t="n">
         <v>3</v>
@@ -5262,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.7585</v>
+        <v>0.8087</v>
       </c>
       <c r="R71" t="n">
         <v>4.268</v>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -5324,13 +5324,13 @@
         <v>0.49</v>
       </c>
       <c r="O72" t="n">
-        <v>0.3435</v>
+        <v>0.3465</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.3813</v>
+        <v>0.4085</v>
       </c>
       <c r="R72" t="n">
         <v>4.268</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -5392,13 +5392,13 @@
         <v>0.15</v>
       </c>
       <c r="O73" t="n">
-        <v>0.1905</v>
+        <v>0.2325</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.3813</v>
+        <v>0.3135</v>
       </c>
       <c r="R73" t="n">
         <v>4.002</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="L74" t="n">
         <v>0.43</v>
@@ -5460,13 +5460,13 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.147</v>
+        <v>0.2517</v>
       </c>
       <c r="R74" t="n">
         <v>2.186</v>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="L75" t="n">
         <v>0.43</v>
@@ -5528,13 +5528,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5790000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.336</v>
+        <v>0.2517</v>
       </c>
       <c r="R75" t="n">
         <v>2.186</v>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="L76" t="n">
         <v>0.47</v>
@@ -5596,13 +5596,13 @@
         <v>0.17</v>
       </c>
       <c r="O76" t="n">
-        <v>0.5319999999999999</v>
+        <v>0.496</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.147</v>
+        <v>0.2517</v>
       </c>
       <c r="R76" t="n">
         <v>2.05</v>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="L77" t="n">
         <v>0.73</v>
@@ -5664,13 +5664,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7645</v>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.368</v>
+        <v>0.3766</v>
       </c>
       <c r="R77" t="n">
         <v>1.197</v>
@@ -5735,10 +5735,10 @@
         <v>0.7615</v>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="R78" t="n">
         <v>1.122</v>
@@ -5800,13 +5800,13 @@
         <v>0.48</v>
       </c>
       <c r="O79" t="n">
-        <v>0.7264999999999999</v>
+        <v>0.7265</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="R79" t="n">
         <v>1.197</v>
@@ -5874,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.0243</v>
+        <v>0.0268</v>
       </c>
       <c r="R80" t="n">
         <v>0.333</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="L81" t="n">
         <v>0.99</v>
@@ -5936,13 +5936,13 @@
         <v>0.67</v>
       </c>
       <c r="O81" t="n">
-        <v>0.87</v>
+        <v>0.873</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.1024</v>
+        <v>0.1048</v>
       </c>
       <c r="R81" t="n">
         <v>0.333</v>
@@ -6010,7 +6010,7 @@
         <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.0243</v>
+        <v>0.0268</v>
       </c>
       <c r="R82" t="n">
         <v>0.312</v>
@@ -6078,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R83" t="n">
         <v>3.019</v>
@@ -6146,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.928</v>
+        <v>0.9497</v>
       </c>
       <c r="R84" t="n">
         <v>3.019</v>
@@ -6214,7 +6214,7 @@
         <v>2</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R85" t="n">
         <v>3.019</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="L86" t="n">
         <v>0.71</v>
@@ -6276,13 +6276,13 @@
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.7425</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.384</v>
+        <v>0.393</v>
       </c>
       <c r="R86" t="n">
         <v>1.249</v>
@@ -6344,13 +6344,13 @@
         <v>0.58</v>
       </c>
       <c r="O87" t="n">
-        <v>0.7474999999999999</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R87" t="n">
         <v>1.249</v>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L88" t="n">
         <v>0.74</v>
@@ -6412,13 +6412,13 @@
         <v>0.15</v>
       </c>
       <c r="O88" t="n">
-        <v>0.6375</v>
+        <v>0.6495</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0912</v>
+        <v>0.0727</v>
       </c>
       <c r="R88" t="n">
         <v>1.171</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="L89" t="n">
         <v>0.96</v>
@@ -6480,13 +6480,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.983</v>
+        <v>0.974</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.0294</v>
+        <v>0.0587</v>
       </c>
       <c r="R89" t="n">
         <v>0.437</v>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L90" t="n">
         <v>0.96</v>
@@ -6548,13 +6548,13 @@
         <v>0.58</v>
       </c>
       <c r="O90" t="n">
-        <v>0.836</v>
+        <v>0.83</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R90" t="n">
         <v>0.41</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L91" t="n">
         <v>0.96</v>
@@ -6616,13 +6616,13 @@
         <v>0.3</v>
       </c>
       <c r="O91" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R91" t="n">
         <v>0.437</v>
@@ -6690,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.2356</v>
+        <v>0.2598</v>
       </c>
       <c r="R92" t="n">
         <v>3.227</v>
@@ -6758,7 +6758,7 @@
         <v>3</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.992</v>
+        <v>1.0152</v>
       </c>
       <c r="R93" t="n">
         <v>3.227</v>
@@ -6826,7 +6826,7 @@
         <v>2</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.2356</v>
+        <v>0.2598</v>
       </c>
       <c r="R94" t="n">
         <v>3.026</v>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L95" t="n">
         <v>0.28</v>
@@ -6888,7 +6888,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.601</v>
+        <v>0.616</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L96" t="n">
         <v>0.28</v>
@@ -6956,7 +6956,7 @@
         <v>0.6</v>
       </c>
       <c r="O96" t="n">
-        <v>0.487</v>
+        <v>0.502</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L97" t="n">
         <v>0.28</v>
@@ -7024,7 +7024,7 @@
         <v>0.31</v>
       </c>
       <c r="O97" t="n">
-        <v>0.3655</v>
+        <v>0.3805</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="L98" t="n">
         <v>0.5600000000000001</v>
@@ -7092,13 +7092,13 @@
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.804</v>
+        <v>0.762</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.119</v>
+        <v>0.2378</v>
       </c>
       <c r="R98" t="n">
         <v>1.77</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="L99" t="n">
         <v>0.5600000000000001</v>
@@ -7160,13 +7160,13 @@
         <v>0.35</v>
       </c>
       <c r="O99" t="n">
-        <v>0.6105</v>
+        <v>0.5805</v>
       </c>
       <c r="P99" t="n">
         <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.119</v>
+        <v>0.2038</v>
       </c>
       <c r="R99" t="n">
         <v>1.77</v>
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="L100" t="n">
         <v>0.5600000000000001</v>
@@ -7228,13 +7228,13 @@
         <v>0.57</v>
       </c>
       <c r="O100" t="n">
-        <v>0.6955000000000001</v>
+        <v>0.6655</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.119</v>
+        <v>0.2038</v>
       </c>
       <c r="R100" t="n">
         <v>1.77</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="L101" t="n">
         <v>0.34</v>
@@ -7296,13 +7296,13 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.7060000000000001</v>
+        <v>0.646</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.168</v>
+        <v>0.3357</v>
       </c>
       <c r="R101" t="n">
         <v>2.498</v>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="L102" t="n">
         <v>0.34</v>
@@ -7364,13 +7364,13 @@
         <v>0.57</v>
       </c>
       <c r="O102" t="n">
-        <v>0.5555</v>
+        <v>0.5135</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.168</v>
+        <v>0.2877</v>
       </c>
       <c r="R102" t="n">
         <v>2.498</v>
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="L103" t="n">
         <v>0.39</v>
@@ -7432,13 +7432,13 @@
         <v>0.25</v>
       </c>
       <c r="O103" t="n">
-        <v>0.4349999999999999</v>
+        <v>0.393</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.168</v>
+        <v>0.2877</v>
       </c>
       <c r="R103" t="n">
         <v>2.342</v>
@@ -7506,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R104" t="n">
         <v>1.093</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="L105" t="n">
         <v>0.76</v>
@@ -7568,13 +7568,13 @@
         <v>0.58</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.669</v>
       </c>
       <c r="P105" t="n">
         <v>3</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.336</v>
+        <v>0.3438</v>
       </c>
       <c r="R105" t="n">
         <v>1.093</v>
@@ -7636,13 +7636,13 @@
         <v>0.29</v>
       </c>
       <c r="O106" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="P106" t="n">
         <v>2</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R106" t="n">
         <v>1.025</v>
